--- a/SpringBoot前沿技术栈/14_SpringBoot-Excel/工作簿ReadDemo1.xlsx
+++ b/SpringBoot前沿技术栈/14_SpringBoot-Excel/工作簿ReadDemo1.xlsx
@@ -1,16 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14040"/>
+    <workbookView windowWidth="29400" windowHeight="14120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="模板1" sheetId="1" r:id="rId1"/>
     <sheet name="模板 2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -26,10 +39,10 @@
     <t>price</t>
   </si>
   <si>
-    <t>游诗成</t>
+    <t>游家纨绔</t>
   </si>
   <si>
-    <t>曹玉敏</t>
+    <t>小曹</t>
   </si>
   <si>
     <t>最强王者</t>
@@ -41,7 +54,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1255,7 +1268,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2">
@@ -1266,7 +1279,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2">
@@ -1316,7 +1329,7 @@
       <c r="A2" s="2">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2">
@@ -1327,7 +1340,7 @@
       <c r="A3" s="2">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2">
